--- a/Meu_Controle_Disciplinas.xlsx
+++ b/Meu_Controle_Disciplinas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/09e1ec09439faba7/E_PUC_ANALISE_DESENVOLVIMENTO_SISTEMAS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\REPOSITORIO-ADS-PUCPR\PUCPR_DisciplinasADS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="163" documentId="8_{19E70320-791E-46B6-B395-808A371C21D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{512FD6B7-434D-4291-AA33-57B6C4180F3E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D325AC8E-BD41-42CC-9DA3-AC4D52207C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" tabRatio="712" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17010" yWindow="780" windowWidth="19185" windowHeight="14445" tabRatio="712" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle" sheetId="15" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="79">
   <si>
     <t>PRIMEIRO ANO</t>
   </si>
@@ -3450,6 +3450,9 @@
       </rPr>
       <t xml:space="preserve"> Teologia e sociedade no paradigma moderno em crise e na pós-modernidade</t>
     </r>
+  </si>
+  <si>
+    <t>em curso</t>
   </si>
 </sst>
 </file>
@@ -3765,7 +3768,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -3884,6 +3887,42 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -3911,65 +3950,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4016,10 +4016,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4317,7 +4313,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="54" t="s">
         <v>38</v>
       </c>
       <c r="C2" s="25">
@@ -4337,7 +4333,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="43"/>
+      <c r="B3" s="55"/>
       <c r="C3" s="25">
         <v>1</v>
       </c>
@@ -4355,7 +4351,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="43"/>
+      <c r="B4" s="55"/>
       <c r="C4" s="25">
         <v>1</v>
       </c>
@@ -4373,7 +4369,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="43"/>
+      <c r="B5" s="55"/>
       <c r="C5" s="25">
         <v>2</v>
       </c>
@@ -4391,7 +4387,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="43"/>
+      <c r="B6" s="55"/>
       <c r="C6" s="25">
         <v>2</v>
       </c>
@@ -4409,7 +4405,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="44"/>
+      <c r="B7" s="56"/>
       <c r="C7" s="25">
         <v>2</v>
       </c>
@@ -4427,7 +4423,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="57" t="s">
         <v>39</v>
       </c>
       <c r="C8" s="25">
@@ -4447,7 +4443,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="46"/>
+      <c r="B9" s="58"/>
       <c r="C9" s="25">
         <v>3</v>
       </c>
@@ -4465,7 +4461,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="46"/>
+      <c r="B10" s="58"/>
       <c r="C10" s="25">
         <v>3</v>
       </c>
@@ -4483,7 +4479,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="46"/>
+      <c r="B11" s="58"/>
       <c r="C11" s="25">
         <v>4</v>
       </c>
@@ -4501,7 +4497,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="46"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="25">
         <v>4</v>
       </c>
@@ -4519,7 +4515,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="47"/>
+      <c r="B13" s="59"/>
       <c r="C13" s="25">
         <v>4</v>
       </c>
@@ -4537,89 +4533,97 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="60">
+      <c r="C14" s="42">
         <v>5</v>
       </c>
-      <c r="D14" s="61">
+      <c r="D14" s="43">
         <v>11100010549</v>
       </c>
-      <c r="E14" s="65" t="s">
+      <c r="E14" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="66">
+      <c r="F14" s="48">
         <v>90</v>
       </c>
-      <c r="G14" s="64"/>
+      <c r="G14" s="46" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="43"/>
-      <c r="C15" s="60">
+      <c r="B15" s="55"/>
+      <c r="C15" s="42">
         <v>5</v>
       </c>
-      <c r="D15" s="61">
+      <c r="D15" s="43">
         <v>11100010561</v>
       </c>
-      <c r="E15" s="67" t="s">
+      <c r="E15" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="66">
+      <c r="F15" s="48">
         <v>90</v>
       </c>
-      <c r="G15" s="64"/>
+      <c r="G15" s="46" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="43"/>
-      <c r="C16" s="60">
+      <c r="B16" s="55"/>
+      <c r="C16" s="42">
         <v>5</v>
       </c>
-      <c r="D16" s="61">
+      <c r="D16" s="43">
         <v>11100010651</v>
       </c>
-      <c r="E16" s="67" t="s">
+      <c r="E16" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="66">
+      <c r="F16" s="48">
         <v>60</v>
       </c>
-      <c r="G16" s="64"/>
+      <c r="G16" s="46" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="43"/>
-      <c r="C17" s="60">
+      <c r="B17" s="55"/>
+      <c r="C17" s="42">
         <v>6</v>
       </c>
-      <c r="D17" s="61">
+      <c r="D17" s="43">
         <v>11100010551</v>
       </c>
-      <c r="E17" s="67" t="s">
+      <c r="E17" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="66">
+      <c r="F17" s="48">
         <v>90</v>
       </c>
-      <c r="G17" s="64"/>
+      <c r="G17" s="46"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="43"/>
-      <c r="C18" s="53">
+      <c r="B18" s="55"/>
+      <c r="C18" s="63">
         <v>6</v>
       </c>
-      <c r="D18" s="54">
+      <c r="D18" s="64">
         <v>11100010562</v>
       </c>
-      <c r="E18" s="58" t="s">
+      <c r="E18" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="59">
+      <c r="F18" s="68">
         <v>75</v>
       </c>
-      <c r="G18" s="57"/>
+      <c r="G18" s="29" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="44"/>
+      <c r="B19" s="56"/>
       <c r="C19" s="25">
         <v>6</v>
       </c>
@@ -4637,89 +4641,97 @@
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="53">
+      <c r="C20" s="63">
         <v>7</v>
       </c>
-      <c r="D20" s="54">
+      <c r="D20" s="64">
         <v>11100010557</v>
       </c>
-      <c r="E20" s="55" t="s">
+      <c r="E20" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="56">
+      <c r="F20" s="66">
         <v>60</v>
       </c>
-      <c r="G20" s="57"/>
+      <c r="G20" s="29" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="49"/>
-      <c r="C21" s="53">
+      <c r="B21" s="61"/>
+      <c r="C21" s="63">
         <v>7</v>
       </c>
-      <c r="D21" s="54">
+      <c r="D21" s="64">
         <v>11100010558</v>
       </c>
-      <c r="E21" s="55" t="s">
+      <c r="E21" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="56">
+      <c r="F21" s="66">
         <v>75</v>
       </c>
-      <c r="G21" s="57"/>
+      <c r="G21" s="29" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="49"/>
-      <c r="C22" s="53">
+      <c r="B22" s="61"/>
+      <c r="C22" s="63">
         <v>7</v>
       </c>
-      <c r="D22" s="54">
+      <c r="D22" s="64">
         <v>11100010560</v>
       </c>
-      <c r="E22" s="58" t="s">
+      <c r="E22" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="59">
+      <c r="F22" s="68">
         <v>75</v>
       </c>
-      <c r="G22" s="57"/>
+      <c r="G22" s="29" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="49"/>
-      <c r="C23" s="60">
+      <c r="B23" s="61"/>
+      <c r="C23" s="42">
         <v>8</v>
       </c>
-      <c r="D23" s="61">
+      <c r="D23" s="43">
         <v>11100010554</v>
       </c>
-      <c r="E23" s="62" t="s">
+      <c r="E23" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="63">
+      <c r="F23" s="45">
         <v>90</v>
       </c>
-      <c r="G23" s="64"/>
+      <c r="G23" s="46"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="50"/>
-      <c r="C24" s="53">
+      <c r="B24" s="62"/>
+      <c r="C24" s="63">
         <v>8</v>
       </c>
-      <c r="D24" s="54">
+      <c r="D24" s="64">
         <v>11100010564</v>
       </c>
-      <c r="E24" s="55" t="s">
+      <c r="E24" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="F24" s="56">
+      <c r="F24" s="66">
         <v>90</v>
       </c>
-      <c r="G24" s="57"/>
+      <c r="G24" s="29" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="54" t="s">
         <v>42</v>
       </c>
       <c r="C25" s="6">
@@ -4737,7 +4749,7 @@
       <c r="G25" s="24"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="43"/>
+      <c r="B26" s="55"/>
       <c r="C26" s="6">
         <v>9</v>
       </c>
@@ -4753,7 +4765,7 @@
       <c r="G26" s="24"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="43"/>
+      <c r="B27" s="55"/>
       <c r="C27" s="6">
         <v>9</v>
       </c>
@@ -4769,7 +4781,7 @@
       <c r="G27" s="24"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="43"/>
+      <c r="B28" s="55"/>
       <c r="C28" s="6">
         <v>10</v>
       </c>
@@ -4785,7 +4797,7 @@
       <c r="G28" s="24"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="43"/>
+      <c r="B29" s="55"/>
       <c r="C29" s="5">
         <v>10</v>
       </c>
@@ -4801,7 +4813,7 @@
       <c r="G29" s="24"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="44"/>
+      <c r="B30" s="56"/>
       <c r="C30" s="5">
         <v>10</v>
       </c>
@@ -4877,20 +4889,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="52"/>
+      <c r="C1" s="53"/>
       <c r="D1" s="30"/>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="52"/>
+      <c r="F1" s="53"/>
       <c r="G1" s="30"/>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="52"/>
+      <c r="I1" s="53"/>
     </row>
     <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="31" t="s">
@@ -4922,10 +4934,10 @@
         <v>49</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="68" t="s">
+      <c r="E3" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="69" t="s">
+      <c r="F3" s="50" t="s">
         <v>50</v>
       </c>
       <c r="G3" s="2"/>
@@ -4944,10 +4956,10 @@
         <v>52</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="68" t="s">
+      <c r="E4" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="69" t="s">
+      <c r="F4" s="50" t="s">
         <v>53</v>
       </c>
       <c r="G4" s="2"/>
@@ -4966,10 +4978,10 @@
         <v>55</v>
       </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="69" t="s">
+      <c r="F5" s="50" t="s">
         <v>56</v>
       </c>
       <c r="G5" s="2"/>
@@ -5032,10 +5044,10 @@
         <v>64</v>
       </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="68" t="s">
+      <c r="E8" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="69" t="s">
+      <c r="F8" s="50" t="s">
         <v>65</v>
       </c>
       <c r="G8" s="2"/>
@@ -5129,7 +5141,7 @@
       <c r="E13" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="70" t="s">
+      <c r="F13" s="51" t="s">
         <v>76</v>
       </c>
       <c r="G13" s="2"/>
@@ -5161,6 +5173,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="aedfdb4c-c335-4a07-83a0-3ecdf77a25e8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0025d61d-20fb-4004-abfc-fc5e958fce31">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Observa_x00e7__x00f5_es xmlns="0025d61d-20fb-4004-abfc-fc5e958fce31" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D8080ED60203BA4C9D929270E4313D65" ma:contentTypeVersion="20" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="5394bf8384765e9d5ac22d305f3c63c7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0025d61d-20fb-4004-abfc-fc5e958fce31" xmlns:ns3="aedfdb4c-c335-4a07-83a0-3ecdf77a25e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b95b07a47de40d951c47c18e2982be02" ns2:_="" ns3:_="">
     <xsd:import namespace="0025d61d-20fb-4004-abfc-fc5e958fce31"/>
@@ -5417,28 +5450,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61FEAD89-5150-4691-9F91-40ACA15CD367}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="0025d61d-20fb-4004-abfc-fc5e958fce31"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="aedfdb4c-c335-4a07-83a0-3ecdf77a25e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="aedfdb4c-c335-4a07-83a0-3ecdf77a25e8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0025d61d-20fb-4004-abfc-fc5e958fce31">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Observa_x00e7__x00f5_es xmlns="0025d61d-20fb-4004-abfc-fc5e958fce31" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B3BBADB-53E8-40B0-9630-61DC37232ACD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67CEEC0A-5A0B-4FB4-84A5-1994D06312FA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5455,29 +5492,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B3BBADB-53E8-40B0-9630-61DC37232ACD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61FEAD89-5150-4691-9F91-40ACA15CD367}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="0025d61d-20fb-4004-abfc-fc5e958fce31"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="aedfdb4c-c335-4a07-83a0-3ecdf77a25e8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>